--- a/exports/PREMIERENE_full_report.xlsx
+++ b/exports/PREMIERENE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>20.36</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1037.05</v>
+        <v>1009.05</v>
       </c>
       <c r="I2" t="n">
         <v>1034.558371858523</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.48</v>
+        <v>-10.95</v>
       </c>
       <c r="L2" t="n">
         <v>14.13</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.29</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45596.55208333334</v>
+        <v>45597.75</v>
       </c>
       <c r="H3" t="n">
-        <v>1029</v>
+        <v>1086.05</v>
       </c>
       <c r="I3" t="n">
         <v>1049.017258890963</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10.36458333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.98</v>
+        <v>-7.63</v>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>8.02</v>
       </c>
       <c r="M3" t="n">
         <v>1.5</v>
       </c>
       <c r="N3" t="n">
-        <v>4.75</v>
+        <v>5.54</v>
       </c>
       <c r="O3" t="n">
         <v>-3.38</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>12.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1125</v>
+        <v>1028.4</v>
       </c>
       <c r="I4" t="n">
         <v>1063.90006815114</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.802083333333333</v>
+        <v>9.635416666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>3.59</v>
+        <v>-5.31</v>
       </c>
       <c r="L4" t="n">
-        <v>4.93</v>
+        <v>7.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="N4" t="n">
         <v>8.06</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45615.55208333334</v>
+        <v>45617.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1086.9</v>
+        <v>1109.35</v>
       </c>
       <c r="I5" t="n">
         <v>1105.179423891584</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.69</v>
+        <v>-7.87</v>
       </c>
       <c r="L5" t="n">
         <v>10.65</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.46</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1307</v>
+        <v>1238</v>
       </c>
       <c r="I6" t="n">
         <v>1250.425835665089</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>17.82</v>
+        <v>11.6</v>
       </c>
       <c r="L6" t="n">
         <v>5.35</v>
@@ -783,7 +854,7 @@
         <v>2.76</v>
       </c>
       <c r="N6" t="n">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="O6" t="n">
         <v>-0.47</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>11.61</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>955</v>
+        <v>1042</v>
       </c>
       <c r="I7" t="n">
         <v>1031.37131935325</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>22.86</v>
+        <v>15.83</v>
       </c>
       <c r="L7" t="n">
         <v>5.4</v>
       </c>
       <c r="M7" t="n">
-        <v>4.02</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>6.88</v>
+        <v>8.69</v>
       </c>
       <c r="O7" t="n">
         <v>-4.15</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>17.05</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>980</v>
+        <v>927.2</v>
       </c>
       <c r="I8" t="n">
         <v>929.0615323934874</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.95</v>
+        <v>-11.02</v>
       </c>
       <c r="L8" t="n">
-        <v>6.28</v>
+        <v>11.19</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>4.76</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="n">
         <v>8.69</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>17.15</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>889.85</v>
+        <v>916.65</v>
       </c>
       <c r="I9" t="n">
         <v>908.9390215476789</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K9" t="n">
-        <v>4.03</v>
+        <v>1.14</v>
       </c>
       <c r="L9" t="n">
         <v>10.06</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.07</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>992.15</v>
+        <v>975</v>
       </c>
       <c r="I10" t="n">
         <v>975.195334684887</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>8.24</v>
+        <v>6.37</v>
       </c>
       <c r="L10" t="n">
         <v>1.69</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.73</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45790.38541666666</v>
+        <v>45790.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1008.5</v>
+        <v>1018.2</v>
       </c>
       <c r="I11" t="n">
         <v>1012.917173563494</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.44</v>
+        <v>-4.43</v>
       </c>
       <c r="L11" t="n">
-        <v>4.51</v>
+        <v>5.13</v>
       </c>
       <c r="M11" t="n">
         <v>4.1</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>1042.8</v>
+        <v>1021</v>
       </c>
       <c r="I12" t="n">
         <v>1031.662228584546</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>2.42</v>
+        <v>0.27</v>
       </c>
       <c r="L12" t="n">
         <v>1.11</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.57</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1045</v>
+        <v>1061</v>
       </c>
       <c r="I13" t="n">
         <v>1051.149902673753</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.35</v>
+        <v>-3.92</v>
       </c>
       <c r="L13" t="n">
-        <v>3.53</v>
+        <v>5.03</v>
       </c>
       <c r="M13" t="n">
         <v>1.86</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1052</v>
+        <v>1043.6</v>
       </c>
       <c r="I14" t="n">
         <v>1047.229994008876</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.85</v>
+        <v>-1.64</v>
       </c>
       <c r="L14" t="n">
         <v>2.83</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.53</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1038</v>
+        <v>1066.5</v>
       </c>
       <c r="I15" t="n">
         <v>1042.028173635133</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K15" t="n">
-        <v>0.54</v>
+        <v>-2.19</v>
       </c>
       <c r="L15" t="n">
         <v>7.58</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.78</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1027.8</v>
+        <v>1013.7</v>
       </c>
       <c r="I16" t="n">
         <v>1017.852544670765</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.63</v>
+        <v>-4.95</v>
       </c>
       <c r="L16" t="n">
-        <v>4.12</v>
+        <v>5.14</v>
       </c>
       <c r="M16" t="n">
         <v>0.48</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.91</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1057</v>
+        <v>1074</v>
       </c>
       <c r="I17" t="n">
         <v>1064.805603021418</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.27</v>
+        <v>-5.95</v>
       </c>
       <c r="L17" t="n">
-        <v>5.25</v>
+        <v>6.54</v>
       </c>
       <c r="M17" t="n">
         <v>0.9</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>6.23</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1035.9</v>
+        <v>1010.6</v>
       </c>
       <c r="I18" t="n">
         <v>1034.078897999348</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.55</v>
+        <v>-5.9</v>
       </c>
       <c r="L18" t="n">
-        <v>4.53</v>
+        <v>6.1</v>
       </c>
       <c r="M18" t="n">
         <v>0.23</v>
       </c>
       <c r="N18" t="n">
-        <v>2.37</v>
+        <v>3.13</v>
       </c>
       <c r="O18" t="n">
         <v>0.26</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.44</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46006.38541666666</v>
+        <v>46006.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>908.9</v>
+        <v>931.05</v>
       </c>
       <c r="I19" t="n">
         <v>918.2910631989364</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>10.06</v>
+        <v>7.87</v>
       </c>
       <c r="L19" t="n">
         <v>6.13</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>856</v>
+        <v>843.3</v>
       </c>
       <c r="I20" t="n">
         <v>851.336821907494</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.06</v>
+        <v>-9.42</v>
       </c>
       <c r="L20" t="n">
-        <v>8.26</v>
+        <v>9.56</v>
       </c>
       <c r="M20" t="n">
         <v>0.09</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>738</v>
+        <v>797.15</v>
       </c>
       <c r="I21" t="n">
         <v>772.8895596746802</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>12.49</v>
+        <v>5.47</v>
       </c>
       <c r="L21" t="n">
         <v>4.53</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6.39</v>
+        <v>7.11</v>
       </c>
       <c r="O21" t="n">
         <v>-0.82</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.85</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>759.65</v>
+        <v>748.9</v>
       </c>
       <c r="I22" t="n">
         <v>754.3886828348159</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.7</v>
+        <v>-6.05</v>
       </c>
       <c r="L22" t="n">
         <v>6.76</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.53</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46091.55208333334</v>
+        <v>46092.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>748</v>
+        <v>776.55</v>
       </c>
       <c r="I23" t="n">
         <v>771.6716305853874</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>0.12</v>
+        <v>-3.69</v>
       </c>
       <c r="L23" t="n">
-        <v>4.81</v>
+        <v>5.47</v>
       </c>
       <c r="M23" t="n">
         <v>1.24</v>
       </c>
       <c r="N23" t="n">
-        <v>4.03</v>
+        <v>4.56</v>
       </c>
       <c r="O23" t="n">
         <v>-1.6</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.77</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1002.5</v>
+        <v>969.1</v>
       </c>
       <c r="I24" t="n">
         <v>976.6395889783026</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K24" t="n">
-        <v>29.1</v>
+        <v>24.8</v>
       </c>
       <c r="L24" t="n">
         <v>3.71</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.67</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46169.38541666666</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1025.2</v>
+        <v>1054.7</v>
       </c>
       <c r="I25" t="n">
         <v>1026.807498878067</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.79</v>
+        <v>-8.83</v>
       </c>
       <c r="L25" t="n">
-        <v>7.11</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>2.56</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.97</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46224.55208333334</v>
+        <v>46225.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1045</v>
+        <v>1020.8</v>
       </c>
       <c r="I26" t="n">
         <v>1044.16669856084</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>55</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.92</v>
+        <v>-3.21</v>
       </c>
       <c r="L26" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.41</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1041</v>
+        <v>1048.8</v>
       </c>
       <c r="I27" t="n">
         <v>1045.770917123004</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.98</v>
+        <v>-2.74</v>
       </c>
       <c r="L27" t="n">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="M27" t="n">
         <v>1.13</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>6.3</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1029</v>
+        <v>1003.4</v>
       </c>
       <c r="I28" t="n">
         <v>1003.751143710964</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.89</v>
+        <v>-4.33</v>
       </c>
       <c r="L28" t="n">
-        <v>4.41</v>
+        <v>4.71</v>
       </c>
       <c r="M28" t="n">
         <v>0.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>0.67</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.58</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46309.38541666666</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>925.2</v>
+        <v>929</v>
       </c>
       <c r="I29" t="n">
         <v>927.0209118445025</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>7.79</v>
+        <v>7.41</v>
       </c>
       <c r="L29" t="n">
         <v>3.65</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>900</v>
+        <v>874.1</v>
       </c>
       <c r="I30" t="n">
         <v>874.5762668415473</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.12</v>
+        <v>-5.91</v>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>5.96</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="O30" t="n">
         <v>2.46</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2211,6 +2582,12 @@
       <c r="Q31" t="n">
         <v>10</v>
       </c>
+      <c r="R31" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3225,7 +3602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="6">
@@ -3235,7 +3612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
@@ -3245,7 +3622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -3255,7 +3632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9">
@@ -3265,7 +3642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="10">
@@ -3275,7 +3652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -3315,7 +3692,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.81</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="15">
@@ -3325,7 +3702,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.33</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="16">
@@ -3335,7 +3712,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.31</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="17">
@@ -3345,7 +3722,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.1</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="18">
@@ -3355,7 +3732,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -3365,7 +3742,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.37</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="20">
@@ -3375,7 +3752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.53</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="21">
@@ -3395,7 +3772,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -3405,7 +3782,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -3415,7 +3792,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="25">
@@ -3425,7 +3802,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="26">
@@ -3435,7 +3812,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.44</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="27">
@@ -3455,7 +3832,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
